--- a/building_inventory.xlsx
+++ b/building_inventory.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,78 +500,195 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IMG_4623.JPEG</t>
+          <t>IMG_4620.JPEG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.56676388888889</v>
+        <v>21.56687222222222</v>
       </c>
       <c r="C6" t="n">
-        <v>-88.23480277777777</v>
+        <v>-88.23479444444445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IMG_4624.JPEG</t>
+          <t>IMG_4623.JPEG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.56626388888889</v>
+        <v>21.56676388888889</v>
       </c>
       <c r="C7" t="n">
-        <v>-88.23488611111111</v>
+        <v>-88.23480277777777</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IMG_4649.JPEG</t>
+          <t>IMG_4624.JPEG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.56393333333333</v>
+        <v>21.56626388888889</v>
       </c>
       <c r="C8" t="n">
-        <v>-88.23265833333333</v>
+        <v>-88.23488611111111</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IMG_4651.JPEG</t>
+          <t>IMG_4625.JPEG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.564375</v>
+        <v>21.56573611111111</v>
       </c>
       <c r="C9" t="n">
-        <v>-88.23253611111112</v>
+        <v>-88.23485555555555</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IMG_4652.JPEG</t>
+          <t>IMG_4628.JPEG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.56549722222222</v>
+        <v>21.56538055555556</v>
       </c>
       <c r="C10" t="n">
-        <v>-88.23234444444445</v>
+        <v>-88.23509166666666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>IMG_4629.JPEG</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>21.56484444444445</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-88.23518333333334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IMG_4642.JPEG</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>21.56109166666667</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-88.23599166666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IMG_4644.JPEG</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>21.56034722222222</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-88.23448055555555</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IMG_4645.JPEG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>21.56035833333333</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-88.23446666666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IMG_4646.JPEG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>21.56033055555556</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-88.23408611111111</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IMG_4649.JPEG</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>21.56393333333333</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-88.23265833333333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IMG_4650.JPEG</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>21.56396388888889</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-88.23265833333333</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IMG_4651.JPEG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>21.564375</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-88.23253611111112</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IMG_4652.JPEG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>21.56549722222222</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-88.23234444444445</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>IMG_4653.JPEG</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B20" t="n">
         <v>21.56631944444445</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C20" t="n">
         <v>-88.23204722222222</v>
       </c>
     </row>
